--- a/tests/SafeOpenXml.Tests/Examples/DefinedNames/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DefinedNames/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R728083428e4f439d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4c04ad8be1d64778"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="TaxRate">Sheet1!$A$1</x:definedName>

--- a/tests/SafeOpenXml.Tests/Examples/DefinedNames/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DefinedNames/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4c04ad8be1d64778"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re093274815794d29"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="TaxRate">Sheet1!$A$1</x:definedName>

--- a/tests/SafeOpenXml.Tests/Examples/DefinedNames/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DefinedNames/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re093274815794d29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R63caff4463114cf7"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="TaxRate">Sheet1!$A$1</x:definedName>

--- a/tests/SafeOpenXml.Tests/Examples/DefinedNames/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DefinedNames/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R63caff4463114cf7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re1be1ee5d9894f11"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="TaxRate">Sheet1!$A$1</x:definedName>

--- a/tests/SafeOpenXml.Tests/Examples/DefinedNames/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DefinedNames/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re1be1ee5d9894f11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R802b96e7524640e9"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="TaxRate">Sheet1!$A$1</x:definedName>

--- a/tests/SafeOpenXml.Tests/Examples/DefinedNames/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DefinedNames/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R802b96e7524640e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re52a199909d04a52"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="TaxRate">Sheet1!$A$1</x:definedName>

--- a/tests/SafeOpenXml.Tests/Examples/DefinedNames/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DefinedNames/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re52a199909d04a52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1fa904efe39f437c"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="TaxRate">Sheet1!$A$1</x:definedName>

--- a/tests/SafeOpenXml.Tests/Examples/DefinedNames/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DefinedNames/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1fa904efe39f437c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4d7730fe01004030"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="TaxRate">Sheet1!$A$1</x:definedName>

--- a/tests/SafeOpenXml.Tests/Examples/DefinedNames/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DefinedNames/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4d7730fe01004030"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9136da0e124d4efe"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="TaxRate">Sheet1!$A$1</x:definedName>

--- a/tests/SafeOpenXml.Tests/Examples/DefinedNames/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DefinedNames/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9136da0e124d4efe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf9da2519ac4f4f76"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="TaxRate">Sheet1!$A$1</x:definedName>

--- a/tests/SafeOpenXml.Tests/Examples/DefinedNames/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DefinedNames/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf9da2519ac4f4f76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcb8a8e6e496e445e"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="TaxRate">Sheet1!$A$1</x:definedName>

--- a/tests/SafeOpenXml.Tests/Examples/DefinedNames/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DefinedNames/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcb8a8e6e496e445e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb995adba085847a2"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="TaxRate">Sheet1!$A$1</x:definedName>
